--- a/data/dividends_info_20261026.xlsx
+++ b/data/dividends_info_20261026.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>39.84999847412109</v>
+        <v>40.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2258469346202026</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="J2" t="n">
         <v>140</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>58.65000152587891</v>
+        <v>59.90000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.193520855564053</v>
+        <v>1.168614327493089</v>
       </c>
       <c r="J3" t="n">
         <v>119</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7692307974459868</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J5" t="n">
         <v>49</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39.84999847412109</v>
+        <v>40.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2258469346202026</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="J6" t="n">
         <v>49</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>26.93000030517578</v>
+        <v>27.15500068664551</v>
       </c>
       <c r="I7" t="n">
-        <v>1.708132175221665</v>
+        <v>1.693978966556323</v>
       </c>
       <c r="J7" t="n">
         <v>42</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.065000057220459</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I8" t="n">
-        <v>3.728813455997861</v>
+        <v>3.756097648343753</v>
       </c>
       <c r="J8" t="n">
         <v>28</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>49.54000091552734</v>
+        <v>49.72000122070312</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6257569525050948</v>
+        <v>0.6234915373874081</v>
       </c>
       <c r="J9" t="n">
         <v>28</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>26.93000030517578</v>
+        <v>27.15500068664551</v>
       </c>
       <c r="I10" t="n">
-        <v>1.002599320238803</v>
+        <v>0.9942920021091463</v>
       </c>
       <c r="J10" t="n">
         <v>28</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>26.06999969482422</v>
+        <v>26.6200008392334</v>
       </c>
       <c r="I11" t="n">
-        <v>2.263137732668002</v>
+        <v>2.216378592785164</v>
       </c>
       <c r="J11" t="n">
         <v>28</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>10.19999980926514</v>
+        <v>10.07999992370605</v>
       </c>
       <c r="I12" t="n">
-        <v>2.058823567910729</v>
+        <v>2.083333349101758</v>
       </c>
       <c r="J12" t="n">
         <v>21</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.980000019073486</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>3.344481594683792</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J13" t="n">
         <v>21</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.599999904632568</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I14" t="n">
-        <v>1.250000021287374</v>
+        <v>1.228070216532597</v>
       </c>
       <c r="J14" t="n">
         <v>14</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7.670000076293945</v>
+        <v>7.940000057220459</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7822685710974765</v>
+        <v>0.7556675008514305</v>
       </c>
       <c r="J15" t="n">
         <v>14</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10.26000022888184</v>
+        <v>10.21000003814697</v>
       </c>
       <c r="I16" t="n">
-        <v>4.483430699203134</v>
+        <v>4.505386858778955</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7692307974459868</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J18" t="n">
         <v>-7</v>
@@ -1500,7 +1500,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -1544,14 +1544,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1595,14 +1595,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -1646,14 +1646,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1663,14 +1663,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1850,14 +1850,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2088,14 +2088,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2156,14 +2156,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2173,14 +2173,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2190,14 +2190,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2207,14 +2207,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2282,7 +2282,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2292,14 +2292,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2309,14 +2309,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2326,14 +2326,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2350,7 +2350,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2360,14 +2360,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2384,7 +2384,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2411,14 +2411,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2496,14 +2496,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2520,7 +2520,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2530,14 +2530,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2622,7 +2622,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2649,14 +2649,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2700,14 +2700,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2717,14 +2717,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2887,14 +2887,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2928,7 +2928,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3013,7 +3013,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3047,7 +3047,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3098,7 +3098,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3115,7 +3115,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3166,7 +3166,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3183,7 +3183,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3200,7 +3200,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3210,14 +3210,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3261,14 +3261,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3285,7 +3285,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3312,14 +3312,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3370,7 +3370,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3387,7 +3387,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3397,14 +3397,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3431,14 +3431,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3455,7 +3455,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3465,14 +3465,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3482,14 +3482,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3499,14 +3499,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3516,14 +3516,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3540,7 +3540,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3550,14 +3550,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3608,7 +3608,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3635,14 +3635,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3669,14 +3669,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3686,14 +3686,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3710,7 +3710,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3727,7 +3727,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3754,14 +3754,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3771,14 +3771,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3788,14 +3788,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3812,7 +3812,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3829,7 +3829,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3880,7 +3880,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3897,7 +3897,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3914,7 +3914,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3941,14 +3941,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3958,14 +3958,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3975,14 +3975,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3999,7 +3999,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4016,7 +4016,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4033,7 +4033,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4050,7 +4050,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4084,7 +4084,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4101,7 +4101,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4111,14 +4111,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4128,14 +4128,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4145,14 +4145,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4169,7 +4169,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4179,14 +4179,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4196,14 +4196,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4220,7 +4220,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4230,14 +4230,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4254,7 +4254,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4264,14 +4264,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4288,7 +4288,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4298,14 +4298,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4322,7 +4322,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4339,7 +4339,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4356,7 +4356,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4373,7 +4373,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4383,14 +4383,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4407,7 +4407,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4424,7 +4424,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4441,7 +4441,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4458,7 +4458,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4475,7 +4475,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4492,7 +4492,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4509,7 +4509,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4526,7 +4526,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4536,14 +4536,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4560,7 +4560,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4577,7 +4577,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4594,7 +4594,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4604,14 +4604,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4628,7 +4628,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4645,7 +4645,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4662,7 +4662,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4689,14 +4689,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4713,7 +4713,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4730,7 +4730,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4747,7 +4747,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4764,7 +4764,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4781,7 +4781,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4815,7 +4815,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4866,7 +4866,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4883,7 +4883,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4900,7 +4900,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4910,14 +4910,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4934,7 +4934,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4985,7 +4985,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5002,7 +5002,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5012,14 +5012,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5036,7 +5036,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5063,14 +5063,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5080,14 +5080,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5121,7 +5121,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5131,14 +5131,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5148,14 +5148,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5172,7 +5172,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5182,14 +5182,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5199,14 +5199,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5216,14 +5216,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5240,7 +5240,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5257,7 +5257,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5291,7 +5291,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5301,14 +5301,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5318,14 +5318,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5376,7 +5376,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5410,7 +5410,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5444,7 +5444,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5461,7 +5461,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5478,7 +5478,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5488,14 +5488,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5522,14 +5522,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5682,7 +5682,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5699,7 +5699,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5709,14 +5709,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -5741,104 +5741,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0003132476</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-12-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-12-09</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>26.93000030517578</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1.708132175221665</v>
-      </c>
-      <c r="I2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5849,44 +5754,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>